--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0044.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0044.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Awakening Journey</t>
+          <t>Hành Trình Thức Tỉnh</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Voyage's Beginning</t>
+          <t>Khởi Đầu Hành Trình</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Overdash Club</t>
+          <t>Câu lạc bộ Bay vượt tốc</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Solaris Trở Lại Lần Hai</t>
+          <t>Sự Trở Lại Của Solaris</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Vực Sâu Cõi Ảo Ảnh</t>
+          <t>Vực Sâu Cõi Ảo</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Intensive Training</t>
+          <t>Huấn Luyện Cường Độ Cao</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Bountiful Crescendo</t>
+          <t>Bản Giao Hưởng Dồi Dào</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Chord Cleansing</t>
+          <t>Thanh Tẩy Giai Điệu</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Ascendant Aces</t>
+          <t>Thăng Hoa Tinh Anh</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Daybreak Cuối Cùng</t>
+          <t>Cuối Cùng Cũng Bình Minh</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Con Đường Cô Đơn</t>
+          <t>Con Đường Cô Độc</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Nấu luyện Hợp kim</t>
+          <t>Nấu Luyện Hợp Kim</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Alloy Smelt II</t>
+          <t>Nấu Luyện Hợp Kim II</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Echo Hunters</t>
+          <t>Thợ Săn Tiếng Vọng</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Wuthering Exploration</t>
+          <t>Thám Hiểm Vực Gió</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Chuyện Kể Từ Núi Firmament</t>
+          <t>Những Câu Chuyện từ Núi Firmament</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Chiến Dịch Lollo</t>
+          <t>Chiến dịch Lollo</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Vực Sâu Cõi Ảo Ảnh</t>
+          <t>Vực Sâu Cõi Ảo</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Dreams Ablaze in Darkness</t>
+          <t>Giấc Mộng Cháy Đen</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>KU Neighborhood Assistant</t>
+          <t>Trợ Lý Khu Phố KU</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>KU Neighborhood Assistant</t>
+          <t>Trợ Lý Khu Phố KU</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>KU Neighborhood Assistant</t>
+          <t>Trợ Lý Khu Phố KU</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Rewards Check-In Khu dân cư KU</t>
+          <t>Phần Thưởng Điểm Danh Khu Phố KU</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Ku Block Bound Account Verification</t>
+          <t>Xác minh tài khoản liên kết Ku Block</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Xác minh tài khoản liên kết thay đổi Ku Block</t>
+          <t>Xác minh thay đổi tài khoản liên kết Ku Block</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Quà tặng Light Thiên Giới</t>
+          <t>Quà tặng Ánh Sáng Thiên Giới</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Dấu Vết Núi Firmament</t>
+          <t>Dấu vết Núi Firmament</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Lửa Bất Tử</t>
+          <t>Lửa Bất Diệt</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Gifts of Gratitude</t>
+          <t>Mộng Tri Ân</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>By Moon's Grace</t>
+          <t>Nhờ Ân Huệ của Mặt Trăng</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>By Moon's Grace: Summary</t>
+          <t>Nhờ Ân Huệ của Mặt Trăng: Tóm Tắt</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Do Echoids Dream of Electric Sheep?</t>
+          <t>Liệu Echo Có Mơ Về Cừu Điện Không?</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Reprise of Tides</t>
+          <t>Tái Ngộ Thủy Triều</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Hazard Revisited</t>
+          <t>Nguy hiểm Tái hiện</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Pincer Maneuver Warriors I</t>
+          <t>Chiến Binh Mưu Kế Kẹp Nã I</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Pincer Maneuver Warriors II</t>
+          <t>Chiến Binh Mưu Kế Kẹp Nã II</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>TapTap Assistant</t>
+          <t>Trợ Lý TapTap</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>TapTap Account Linking Verification</t>
+          <t>Liên Kết Tài Khoản TapTap - Xác Minh</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>TapTap Assistant</t>
+          <t>Trợ Lý TapTap</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>TapTap Assistant</t>
+          <t>Trợ Lý TapTap</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Wuthering Waves Dev Đội</t>
+          <t>Đội Ngũ Phát Triển Sóng Gió Mạnh Mẽ</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>[Rewards] Rewards sự kiện Wuthering Waves Twitch Drop</t>
+          <t>Phần thưởng Sự Kiện - Wuthering Waves Twitch Drop</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Trợ lý Xác minh Account</t>
+          <t>Trợ lý xác minh tài khoản</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Account Linking Verification</t>
+          <t>Xác minh liên kết tài khoản</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Trợ lý Xác minh Account</t>
+          <t>Trợ lý xác minh tài khoản</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Third-Party Login Authentication</t>
+          <t>Xác thực đăng nhập bên thứ ba</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Wuthering Waves Dev Đội</t>
+          <t>Đội Ngũ Phát Triển Sóng Gió Mạnh Mẽ</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Wuthering Waves Dev Đội</t>
+          <t>Đội Ngũ Phát Triển Sóng Gió Mạnh Mẽ</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Wuthering Waves Dev Đội</t>
+          <t>Đội Ngũ Phát Triển Sóng Gió Mạnh Mẽ</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Wuthering Waves Dev Đội</t>
+          <t>Đội Ngũ Phát Triển Sóng Gió Mạnh Mẽ</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Update mới trong Depths of Illusive Realm</t>
+          <t>Bản cập nhật mới trong Vực Ảo Mộng</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Update mới trong Depths of Illusive Realm</t>
+          <t>Bản cập nhật mới trong Vực Ảo Mộng</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Nhắc Nhở End Sự Kiện</t>
+          <t>Nhắc nhở Kết thúc Sự kiện</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Nhắc Nhở End Sự Kiện</t>
+          <t>Nhắc nhở Kết thúc Sự kiện</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Wuthering Waves Dev Đội</t>
+          <t>Đội Ngũ Phát Triển Sóng Gió Mạnh Mẽ</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Thông báo Nâng Cấp và Bảo Trì Sự Kiện [Reprise of Tides] Dành Cho Người Chơi Quay Lại</t>
+          <t>Thông Báo Nâng Cấp và Bảo Trì Sự Kiện [Hồi Âm Thủy Triều] Dành Cho Người Trở Về</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Gifts of Lunar Radiance</t>
+          <t>Mộng Ánh Trăng Rạng Ngời</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Bản Chất Thật</t>
+          <t>Bản Lĩnh Thật</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Converging Paths</t>
+          <t>Những con đường hội tụ</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Giữa các Vì sao</t>
+          <t>Giữa Ngân Hà</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Nơi Những Vì Sao An Giấc</t>
+          <t>Nơi Sao An Giấc</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Wooly Nhỏ, Cuộc Phiêu Lưu Lớn</t>
+          <t>Cừu Nhỏ, Đại Phiêu Lưu</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Dự báo thời tiết Solaris</t>
+          <t>Dự báo Thời tiết Solaris</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Mô phỏng Chiến đấu Vô tận</t>
+          <t>Mô Phỏng Chiến Đấu Vô Tận</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Lollo Campaign: Rerun</t>
+          <t>Chiến Dịch Lollo: Tái Diễn</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Lollo Campaign: Set Sail</t>
+          <t>Chiến Dịch Lollo: Khởi Hành</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Cái kết của câu chuyện cổ tích</t>
+          <t>Hồi Kết Của Truyện Cổ Tích</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Gifts of Sea Breeze</t>
+          <t>Quà Tặng Gió Biển</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Mê Cung Giấc Mộng</t>
+          <t>Mê Cung Somnium</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Themed Event</t>
+          <t>Sự Kiện Chủ Đề</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Đợt Bán Hàng Thần Tốc Ragunna!</t>
+          <t>Đợt Bán Hàng Ragunna!</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Pioneer Association Themed Event</t>
+          <t>Sự Kiện Chủ Đề Hiệp Hội Tiên Phong</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Pioneer Project</t>
+          <t>Dự Án Tiên Phong</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Beyond Sóng Gió</t>
+          <t>Vượt Qua Những Con Sóng</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Exploration Event</t>
+          <t>Sự Kiện Thám Hiểm</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Những Lối Rẽ Giữa Các Vì Sao</t>
+          <t>Những Ngả Đường Giữa Các Vì Sao</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Companion Story</t>
+          <t>Câu Chuyện Đồng Hành</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Quà Tặng Giấc Mơ Phù Du</t>
+          <t>Mộng Ảo Phù Du</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Tactical Simulacra: Off Tune</t>
+          <t>Bản Sao Chiến Thuật: Lệch Tần</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Parade of Stars</t>
+          <t>Diễu Hành Sao Trời</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Chiến dịch Lollo: Trở lại</t>
+          <t>Chiến Dịch Lollo: Trở Lại</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Chiến dịch Lollo: Xác minh</t>
+          <t>Chiến Dịch Lollo: Xác Minh</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Chiến dịch Lollo: Xác minh</t>
+          <t>Chiến Dịch Lollo: Xác Minh</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Dấu Vết Của Thủy Triều</t>
+          <t>Dấu vết của Thủy Triều</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Next Stop: Rinascita</t>
+          <t>Điểm Đến Tiếp Theo: Rinascita</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>John Wicktorio: Không Nợ Nần Từ Quá Khứ</t>
+          <t>John Wicktorio: Không Nợ Cũ</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Chuyện kể trên đảo</t>
+          <t>Huyền Thoại Quần Đảo</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Phantom Pain</t>
+          <t>Hologram Chiến Thuật: Nỗi Đau Ảo Ảnh</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Nếu Một Night Rainy Có Một Gia Đình</t>
+          <t>Nếu Một Đêm Mưa Gia Đình</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Companion Story</t>
+          <t>Câu Chuyện Đồng Hành</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Đêm Đầy Sao</t>
+          <t>Đêm Ngàn Sao</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Companion Story</t>
+          <t>Câu Chuyện Đồng Hành</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Ngày Ra Khơi, Thuyền Trưởng!</t>
+          <t>Ngày Hành Trình, Thuyền trưởng!</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Companion Story</t>
+          <t>Câu Chuyện Đồng Hành</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Quà Tặng Giai Điệu Vui Tươi</t>
+          <t>Mộng Giai Điệu Vui Tươi</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Dances For Spring's Return</t>
+          <t>Điệu nhảy đón xuân về</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Pincer Maneuver Warriors III</t>
+          <t>Chiến Binh Mưu Kế Kẹp Nã III</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Pincer Maneuver Warriors IV</t>
+          <t>Chiến Binh Mưu Kế Kẹp Nã IV</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Glamour Couture</t>
+          <t>Thời Trang Lộng Lẫy</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Wuthering Waves Dev Đội</t>
+          <t>Đội Ngũ Phát Triển Sóng Gió Mạnh Mẽ</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Nhắc Nhở End Sự Kiện</t>
+          <t>Nhắc nhở Kết thúc Sự kiện</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Ông Già và Cá Voi</t>
+          <t>Lão Già và Cá Voi</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Tactical Simulacra III</t>
+          <t>Bản Sao Chiến Thuật III</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Beyond Sóng Gió</t>
+          <t>Vượt Qua Những Con Sóng</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Beyond Sóng Gió: Rinascita</t>
+          <t>Vượt Qua Những Con Sóng: Rinascita</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Exploration Event</t>
+          <t>Sự Kiện Thám Hiểm</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Exploration Event</t>
+          <t>Sự Kiện Thám Hiểm</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Vùng Đất Than Thở</t>
+          <t>Vùng Đất Than Khóc</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Apex Ragunna</t>
+          <t>Ragunna Đỉnh Cao</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Quà Tặng Nước Xanh</t>
+          <t>Quà tặng Nước Xanh</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Co-op Overdash</t>
+          <t>Quá Tốc Đồng Đội</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Acropolis Documentarian</t>
+          <t>Nhà Biên Ký Acropolis</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Virtual Crisis: Prototype Trials</t>
+          <t>Khủng Hoảng Ảo: Thử Nghiệm Nguyên Mẫu</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Ảo tưởng Ngàn Cánh Cổng</t>
+          <t>Những Ảo Ảnh Ngàn Cánh Cổng</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Avinoleum Travel Atlas</t>
+          <t>Bản Đồ Du Hành Avinoleum</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Exploration Progress</t>
+          <t>Tiến Độ Thám Hiểm</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Septimont Travel Atlas</t>
+          <t>Bản Đồ Du Hành Septimont</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Sanguis Plateaus Travel Atlas</t>
+          <t>Bản Đồ Du Hành Cao Nguyên Sanguis</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Second Coming of Solaris (Ultra)</t>
+          <t>Sự Trở Lại Của Solaris (Cao Cấp)</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Leisure Event</t>
+          <t>Sự Kiện Nhàn Hạ</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Chưa có sẵn</t>
+          <t>Chưa khả dụng</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Wuthering Waves Dev Đội</t>
+          <t>Đội Ngũ Phát Triển Sóng Gió Mạnh Mẽ</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Điệu Nhảy Cho Spring Trở Lại - Unclaimed Rewards</t>
+          <t>Điệu nhảy đón xuân về - Phần thưởng chưa nhận</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Infinite Battle Simulation II</t>
+          <t>Mô Phỏng Chiến Đấu Vô Tận II</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Dreaming Deep</t>
+          <t>Giấc Mơ Sâu Thẳm</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Liên hoan phim Solaris</t>
+          <t>Liên hoan Điện ảnh Solaris</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Ragunna Weather Forecast</t>
+          <t>Dự Báo Thời Tiết Ragunna</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Leisure Event</t>
+          <t>Sự Kiện Nhàn Hạ</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Cubie Derby</t>
+          <t>Đua Cubie</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Giấc Mơ Đêm Thoáng Qua</t>
+          <t>Giấc Mộng Đêm Thoáng Qua</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Đến Lúc Carnevale Rồi!</t>
+          <t>Lễ hội Carnevale đến rồi!</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Invitation code copied</t>
+          <t>Đã sao chép mã mời</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Proceed</t>
+          <t>Tiến lên</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Du ký Ký ức</t>
+          <t>Biên Niên Ký Ức</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Quà Tặng Từ Những Dòng Thủy Lặng</t>
+          <t>Quà Tặng Thủy Triều Lặng</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Quà Tặng Đại Đoàn Viên</t>
+          <t>Mộng Đại Hội Ngộ</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Quà Tặng Những Giai Điệu Du Dương</t>
+          <t>Quà Tặng Khúc Ca Du Dương</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Quà Tặng Tiếng Vỗ Tay</t>
+          <t>Quà tặng Tiếng Vỗ Tay</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Quà Tặng Bản Giao Hưởng Vĩ Đại</t>
+          <t>Mộng Giao Hưởng Vĩ Đại</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Quà Tặng Cuộc Săn Bắt</t>
+          <t>Quà Tặng Săn Bắt</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Quà Tặng Dawn Đến Gần</t>
+          <t>Quà tặng Bình Minh Đến Gần</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Quà Tặng Hổ Phách</t>
+          <t>Quà tặng Hổ Phách</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Quà Tặng Song Mực Tàu</t>
+          <t>Mộng Khúc Ca Mực Tàu</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Quà Tặng Tuần Lễ Tân Sinh Viên</t>
+          <t>Mộng Tuần Lễ Khai Sinh</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Gifts of Soft Snow</t>
+          <t>Quà Tặng Tuyết Mềm</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Quà Tặng Solsworn</t>
+          <t>Quà Tặng Của Solsworn</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Lament Recon: Chiến Binh Solaris</t>
+          <t>Thám Sát Âm Than: Lính Solaris</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Combat Event</t>
+          <t>Sự Kiện Chiến Đấu</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Freeze Frame: Những Khoảnh Khắc Nổi Bật</t>
+          <t>Định Hình: Điểm Nổi Bật Hành Động</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Chụp ảnh chiến đấu</t>
+          <t>Chụp Ảnh Chiến Đấu</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Cube, Cubic và Cubie</t>
+          <t>Khối, Khối Lập Phương và Cubie</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Cubie Derby: Warmup</t>
+          <t>Giải Đua Cubie: Khởi Động</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Tidal Festivities</t>
+          <t>Lễ hội Thủy Triều</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Tidal Festivities</t>
+          <t>Lễ hội Thủy Triều</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Quà Tặng Đại Kỷ Niệm</t>
+          <t>Mộng Đại Lễ</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Nhân vật Thử nghiệm</t>
+          <t>Nhân vật thử nghiệm</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>New Map</t>
+          <t>Bản Đồ Mới</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>New Area</t>
+          <t>Khu Vực Mới</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Companion Story</t>
+          <t>Câu Chuyện Đồng Hành</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Combat Event</t>
+          <t>Sự Kiện Chiến Đấu</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Themed Event</t>
+          <t>Sự Kiện Chủ Đề</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Exploration Event</t>
+          <t>Sự Kiện Thám Hiểm</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Reward Event</t>
+          <t>Sự kiện phần thưởng</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Co-op Event</t>
+          <t>Sự kiện Đồng Đội</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Leisure Event</t>
+          <t>Sự Kiện Nhàn Hạ</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Unlocked at Cấp Liên Minh 2</t>
+          <t>Mở khóa ở Cấp Liên Minh 2</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Mùa Hè Của Bạn Sẽ Không Tàn Phai</t>
+          <t>Mùa Hè Của Ngươi Sẽ Không Bao Giờ Tàn Úa</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Toàn Lực! Hướng Tới Peaks of Prestige</t>
+          <t>Tất Cả Vào Cuộc! Vươn Tới Đỉnh Danh Vọng</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Gilded Nightmarket</t>
+          <t>Chợ Đêm Mạ Vàng</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Combat Event</t>
+          <t>Sự Kiện Chiến Đấu</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Spindrift Task</t>
+          <t>Nhiệm Vụ Gió Bấc</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Solaris New Voyage Celebration</t>
+          <t>Lễ kỷ niệm Hành trình Mới của Solaris</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Lá Cờ Không Bao Giờ Rơi</t>
+          <t>Ngọn Cờ Không Bao Giờ Sụp Đổ</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Virtual Crisis: Frontier Trials</t>
+          <t>Khủng Hoảng Ảo: Thử Thách Biên Giới</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Duelist Challenge</t>
+          <t>Thử Thách Đối Kháng</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Deck Build</t>
+          <t>Xây dựng Bộ bài</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Echo Overview</t>
+          <t>Tổng quan Echo</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Chọn Challenge</t>
+          <t>Chọn Thử Thách</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Endless Challenge</t>
+          <t>Thử Thách Vô Tận</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Medal of Prestige</t>
+          <t>Huy Chương Uy Tín</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Bộ Sưu Tập Echo</t>
+          <t>Thu Thập Tiếng Vọng</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Săn đuổi Tro và Thép</t>
+          <t>Cuộc săn tro tàn và thép lạnh</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Nhiệm Vụ Chính Fast Track Event</t>
+          <t>Sự Kiện Tiến Độ Nhiệm Vụ Chính Nhanh</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Limited-Time Special Login Event</t>
+          <t>Sự Kiện Đăng Nhập Đặc Biệt Giới Hạn</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Overflowing Picture Book</t>
+          <t>Sách Tranh Tràn</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Phantasma Dreamland</t>
+          <t>Vùng Đất Mộng Ảo</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Dấu Chân Cao Nguyên</t>
+          <t>Dấu Vết Cao Nguyên</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Trở Lại Solaris</t>
+          <t>Trở lại Solaris</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Mô phỏng Phòng thủ Thủy triều</t>
+          <t>Mô Phỏng Phòng Thủ Thủy Triều</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Dự án Windrider</t>
+          <t>Dự Án Kỵ Sĩ Gió</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Moonlit Revelation</t>
+          <t>Bí Ẩn Dưới Trăng</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Dấu Ấn Hoang Dã</t>
+          <t>Dấu Vết Hoang Dã</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>COST 4 (Common)</t>
+          <t>CHI PHÍ 4 (Thường)</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>COST 4 (Healing)</t>
+          <t>CHI PHÍ 4 (Hồi Phục)</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>COST 3 (Healing)</t>
+          <t>CHI PHÍ 3 (Hồi Phục)</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Non 5-Star</t>
+          <t>Hạng Không 5 Sao</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>COST 3 (Glacio)</t>
+          <t>CHI PHÍ 3 (Glacio)</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>COST 3 (Fusion)</t>
+          <t>CHI PHÍ 3 (Fusion)</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>COST 3 (Electro)</t>
+          <t>CHI PHÍ 3 (Electro)</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>COST 3 (Aero)</t>
+          <t>CHI PHÍ 3 (Aero)</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>COST 3 (Spectro)</t>
+          <t>CHI PHÍ 3 (Spectro)</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>COST 3 (Havoc)</t>
+          <t>CHI PHÍ 3 (Havoc)</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Quà Tặng Từ Kẻ Lang Thang Mặt Trăng</t>
+          <t>Quà Tặng Kẻ Lang Thang Trăng</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Lollo Campaign: Rising Anew</t>
+          <t>Chiến Dịch Lollo: Trỗi Dậy Mới</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Chiến dịch Lollo: Vị cứu tinh băng giá</t>
+          <t>Chiến Dịch Lollo: Vị Cứu Tinh Băng Giá</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Lời thì thầm của sóng</t>
+          <t>Lời thì thầm của sóng biển</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Septimont Weather Forecast</t>
+          <t>Dự Báo Thời Tiết Septimont</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Wuthering Waves Dev Đội</t>
+          <t>Đội Ngũ Phát Triển Sóng Gió Mạnh Mẽ</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Nhắc Nhở End Sự Kiện</t>
+          <t>Nhắc nhở Kết thúc Sự kiện</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Wuthering Waves Dev Đội</t>
+          <t>Đội Ngũ Phát Triển Sóng Gió Mạnh Mẽ</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Nhắc Nhở End Sự Kiện</t>
+          <t>Nhắc nhở Kết thúc Sự kiện</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Wuthering Waves Dev Đội</t>
+          <t>Đội Ngũ Phát Triển Sóng Gió Mạnh Mẽ</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Nhắc Nhở End Sự Kiện</t>
+          <t>Nhắc nhở Kết thúc Sự kiện</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>New Update Highlight</t>
+          <t>Điểm nổi bật của bản cập nhật mới</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Wuthering Waves Dev Đội</t>
+          <t>Đội Ngũ Phát Triển Sóng Gió Mạnh Mẽ</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Nhắc Nhở End Sự Kiện</t>
+          <t>Nhắc nhở Kết thúc Sự kiện</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Tactical Simulacra: Off Tune</t>
+          <t>Bản Sao Chiến Thuật: Lệch Tần</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Permanent Challenges</t>
+          <t>Các Thử thách Vĩnh viễn</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Recurring Challenges</t>
+          <t>Thử Thách Lặp Lại</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Forbidden Waters</t>
+          <t>Vùng Nước Cấm</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Respawning Waters</t>
+          <t>Suối Tái Sinh</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Khu vực nguy hiểm</t>
+          <t>Khu vực Nguy hiểm</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Non-Hazard Zone</t>
+          <t>Khu Vực Phi Nguy Hiểm</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Ảo tưởng Ngàn Cánh Cổng</t>
+          <t>Những Ảo Ảnh Ngàn Cánh Cổng</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Chuyện Lạ Ở Honami</t>
+          <t>Những Điều Kỳ Lạ Ở Honami</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Combat Event</t>
+          <t>Sự Kiện Chiến Đấu</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Search! Những Mảnh Ghép Của Lahai-Roi</t>
+          <t>Tìm kiếm! Mảnh vỡ Lahai-Roi</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Showcase Event</t>
+          <t>Sự kiện Trưng Bày</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Dấu Hiệu Của Ngôi Sao Lặng Thinh</t>
+          <t>Dấu Hiệu Của Ngôi Sao Lặng Im</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Showcase Event</t>
+          <t>Sự kiện Trưng Bày</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Signs of a Silent Star</t>
+          <t>Dấu Hiệu Của Ngôi Sao Lặng Im</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Unknown Signal</t>
+          <t>Tín Hiệu Lạ</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Previous message not deciphered yet</t>
+          <t>Tin nhắn trước chưa được giải mã</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Không new WavesLine messages</t>
+          <t>Không có tin nhắn WavesLine mới</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Unknown Message Detected</t>
+          <t>Phát hiện tin nhắn lạ</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Decipher</t>
+          <t>Giải mã</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Deciphering Complete</t>
+          <t>Hoàn tất giải mã</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Đã nhận phần thưởng</t>
+          <t>Đã nhận phần thưởng rồi</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Perfect Deciphering</t>
+          <t>Giải Mã Hoàn Hảo</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Redundant Operation</t>
+          <t>Thao Tác Dư Thừa</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Trở về Solaris</t>
+          <t>Trở lại Solaris</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Đỉnh Danh Vọng: Trận tái đấu</t>
+          <t>Đỉnh Vinh Quang: Cuộc Đọ Sức Nảy Lửa</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Featured Event</t>
+          <t>Sự Kiện Nổi Bật</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Đỉnh Danh Vọng: Trận tái đấu</t>
+          <t>Đỉnh Vinh Quang: Cuộc Đọ Sức Nảy Lửa</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Featured Event</t>
+          <t>Sự Kiện Nổi Bật</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Division Tasks</t>
+          <t>Nhiệm Vụ Phân Công</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Đỉnh Danh Vọng: Trận tái đấu</t>
+          <t>Đỉnh Vinh Quang: Cuộc Đọ Sức Nảy Lửa</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Đỉnh Danh Vọng: Trận tái đấu</t>
+          <t>Đỉnh Vinh Quang: Cuộc Đọ Sức Nảy Lửa</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Chiến Dịch: Tái Thiết Biên Cương</t>
+          <t>Chiến dịch: Tái thiết Biên giới</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Vượt Sóng: Lahai-Roi</t>
+          <t>Vượt Qua Những Con Sóng: Lahai-Roi</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Exploration Event</t>
+          <t>Sự Kiện Thám Hiểm</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Bắt Ánh Sao</t>
+          <t>Ghi lại Ánh Sao</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Test Server Training Ground</t>
+          <t>Khu Huấn Luyện Máy Chủ Thử Nghiệm</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Lahai-Roi Pioneers</t>
+          <t>Những Tiên Phong Lahai-Roi</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Nơi Các Vì Sao Rơi Xuống</t>
+          <t>Nơi Sao Rơi Như Mưa</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Doubled Pawns Matrix: Phi Công</t>
+          <t>Ma trận Tốt Đôi: Phi Công</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Synchronization</t>
+          <t>Hologram Chiến Thuật: Đồng Bộ Hóa</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Sứ giả của Thủy Triều New</t>
+          <t>Sứ Giả Của Những Con Sóng Mới</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Đua Startorch</t>
+          <t>Đua Xe Sao Chổi</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Tăng tốc! Bolt &amp; Blitz!</t>
+          <t>Tốc Lực Tối Đa! Sấm Chớp &amp; Tia Lửa!</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Dimmr Travelogue</t>
+          <t>Nhật Ký Hành Trình Dimmr</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Card Collection</t>
+          <t>Bộ sưu tập Thẻ</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Startorch Dành Cho Bạn</t>
+          <t>Sao Chổi Dành Cho Bạn</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Kìm Hãm! Hỗn Loạn Di Cư!</t>
+          <t>Thuần Phục! Hỗn Loạn Di Cư!</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Lollo Campaign: Implementation</t>
+          <t>Chiến Dịch Lollo: Thực Thi</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Mạch Đất Băng Giá</t>
+          <t>Mạch Đất Vùng Băng Giá</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>TERM-X: Outreach</t>
+          <t>TERM-X: Truyền Tin</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Bay theo nhịp điệu</t>
+          <t>Bay theo Nhịp Điệu</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21154,7 +21154,8 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>[Reminder] Substat Modification Pending Finalization</t>
+          <t>[
+Nhắc Nhở] Chỉnh Sửa Chỉ Số Phụ Chưa Hoàn Tất</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21224,7 +21225,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Hiệp sĩ Hoang dã</t>
+          <t>Hiệp Sĩ Hoang Dã</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21295,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>And Other Vật phẩm</t>
+          <t>Và Những Vật Phẩm Khác</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21434,7 +21435,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Tìm trạm vũ trụ rơi trong Nhiệm Vụ Chính "The Star That Voyages Far" để mở khóa</t>
+          <t>Tìm trạm vũ trụ đã rơi trong Nhiệm Vụ Chính "Ngôi Sao Viễn Du" để mở khóa</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21504,7 +21505,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Tìm trạm vũ trụ rơi trong Nhiệm Vụ Chính "The Star That Voyages Far" để mở khóa</t>
+          <t>Tìm trạm vũ trụ đã rơi trong Nhiệm Vụ Chính "Ngôi Sao Viễn Du" để mở khóa</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21714,7 +21715,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Vực Sâu Cõi Ảo Ảnh</t>
+          <t>Vực Sâu Cõi Ảo</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21785,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Chromatic Fantasy</t>
+          <t>Ảo Ảnh Sắc Màu</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21855,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Vực Thẳm Cõi Ảo: Chromatic Fantasy</t>
+          <t>Tổ Tacet Ảo Ảnh: Giấc Mộng Sắc Màu</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21925,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Vào Chương trình Ký ức!</t>
+          <t>Tiến vào Chương Trình Ký Ức!</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21994,7 +21995,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Second Coming of Solaris: Collab Season</t>
+          <t>Sự Trở Lại Của Solaris: Mùa Cộng Tác</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22064,7 +22065,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Lollo Express: Promise Delivered</t>
+          <t>Lollo Express: Lời Hứa Đã Thực Hiện</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22134,7 +22135,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Quà Tặng Đại Kỷ Niệm</t>
+          <t>Mộng Đại Lễ</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22205,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Beyond the Waves: Roya Frostlands</t>
+          <t>Vượt Qua Những Con Sóng: Roya Frostlands</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22275,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Nảy Bóng Sao</t>
+          <t>Vụ nổ sao</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22345,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Wuthering Waves Dev Đội</t>
+          <t>Đội Ngũ Phát Triển Sóng Gió Mạnh Mẽ</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22415,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Nhắc Nhở End Sự Kiện</t>
+          <t>Nhắc nhở Kết thúc Sự kiện</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22485,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Quà Tặng Starlight</t>
+          <t>Quà Tặng Ánh Sao</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22555,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Crossworld Sync: Pt. 1</t>
+          <t>Đồng Bộ Thế Giới: Phần 1</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22625,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Crossworld Sync: Pt. 2</t>
+          <t>Đồng Bộ Thế Giới: Phần 2</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22694,7 +22695,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Bouquet</t>
+          <t>Bó Hoa</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22764,7 +22765,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Elegant</t>
+          <t>Thanh Lịch</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22835,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>I'm… fine…</t>
+          <t>Tôi... không sao...</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22904,7 +22905,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Một người mẹ và đứa con mới sinh đang trốn trong đống đổ nát, cố tránh khỏi những sinh vật chết chóc</t>
+          <t>Một người mẹ và đứa con mới sinh đang trốn trong đống đổ nát, cố gắng tránh khỏi những sinh vật chết chóc.</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22974,7 +22975,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Với một luồng năng lượng bùng nổ, Sentinel của chúng ta đã xua tan những điều ác xung quanh</t>
+          <t>Với một luồng năng lượng bùng nổ, Sentinel của chúng ta đã xua tan mọi tà ác xung quanh.</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23044,7 +23045,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Nhưng đáng buồn là, đã quá muộn</t>
+          <t>Nhưng tiếc thay, đã quá muộn rồi.</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -24304,7 +24305,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Bạn đưa người phiêu lưu đang hôn mê và trở về Hongzhen cùng Changli</t>
+          <t>Bạn bế người thám hiểm đang hôn mê và trở về Hồng Chân cùng Changli.</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24514,7 +24515,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Nơi đâu cô nhìn cũng thấy bi kịch tràn lan</t>
+          <t>Nơi cô nhìn đến đâu cũng chỉ thấy bi kịch tràn lan.</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24585,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>As Lament engulfed the globe</t>
+          <t>Khi Lament nuốt chửng địa cầu</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24654,7 +24655,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Một thế giới bị xé nát bởi quái vật, đầy những linh hồn vô gia cư</t>
+          <t>Một thế giới bị xé nát bởi quái vật, đầy rẫy những linh hồn vô gia cư.</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24725,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Với máu của chính mình làm ngọn lửa, cô xua tan cái lạnh</t>
+          <t>Lấy máu mình làm ngọn lửa, nàng xua tan đi giá lạnh.</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24795,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Trong thế giới hỗn loạn này, sinh mạng mong manh như phù du</t>
+          <t>Trong thế giới hỗn loạn này, sinh mạng mong manh như phù du.</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24865,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Cô không thể kiệt sức để cứu những người trước mắt mình</t>
+          <t>Cô ấy không thể kiệt sức để cứu những người trước mắt mình.</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24934,7 +24935,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Nhưng she must endure</t>
+          <t>Nhưng cô ấy phải chịu đựng...</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25005,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>To ignite a brighter tomorrow</t>
+          <t>Để thắp lên một ngày mai rực rỡ hơn</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25074,7 +25075,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Cô ấy dùng trí thông minh để tránh khỏi tổn hại, bước đi cẩn trọng trên lưỡi dao</t>
+          <t>Cô ấy dùng trí thông minh để tránh né nguy hiểm, bước đi trên lưỡi dao mà vẫn thận trọng.</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25145,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Alone, yet maturing through stumbles</t>
+          <t>Cô đơn, nhưng trưởng thành qua từng vấp ngã...</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25215,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Sau này, cô trở thành "người thầy" của người khác</t>
+          <t>Sau này, cô ấy trở thành "giáo viên" của người khác.</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25285,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Để dẫn dắt lương tâm và đảm bảo sự thịnh vượng cho nhân dân</t>
+          <t>Để dẫn dắt lương tâm, và đảm bảo sự thịnh vượng cho nhân dân</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25355,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Để tiếp nối những lời dạy đã mất của các bậc hiền nhân xưa, và thiết lập hòa bình cho tất cả</t>
+          <t>Để tiếp nối những lời dạy đã thất truyền của các bậc hiền nhân, và thiết lập hòa bình cho tất cả.</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25425,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>—Một ngày nào đó, tương lai của sự thịnh vượng và hòa bình vĩnh cửu sẽ đến</t>
+          <t>—Một ngày nào đó, tương lai thịnh vượng và hòa bình vĩnh cửu sẽ đến</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25495,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Ông Zou lại kể một câu chuyện khác…</t>
+          <t>Ông nội Zou lại kể chuyện nữa rồi…</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25565,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Làm sao để nói với ông ấy đây…</t>
+          <t>Làm sao để báo tin này cho cậu ấy đây…</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25635,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Tôi thật sự không muốn là người ngăn cản ông ấy theo đuổi ước mơ, nên tôi…</t>
+          <t>Mình thật sự không muốn trở thành người ngăn cản cậu ấy theo đuổi ước mơ, nên mình...</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25704,7 +25705,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>About Grandpa Zou…</t>
+          <t>Về Ông Zou…</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25774,7 +25775,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>About Changli's future plans…</t>
+          <t>Về kế hoạch tương lai của Changli…</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -26124,7 +26125,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>*Shake your head*</t>
+          <t>*Lắc đầu*</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26194,7 +26195,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Vô vàn khả năng███Bản ghi███Nhiệm vụ của tôi…</t>
+          <t>Vô vàn khả năng███Bản ghi███Nhiệm vụ của ta…</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26264,7 +26265,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Scraps' executioners███Không, no██████…</t>
+          <t>Những kẻ hành quyết của Scraps███Không, không██████…</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26404,7 +26405,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>(Draw kiếm)</t>
+          <t>Rút kiếm ra!</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26475,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>(Draw kiếm)</t>
+          <t>Rút kiếm ra!</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26544,7 +26545,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>What was that…</t>
+          <t>Cái gì thế nhỉ…</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26614,7 +26615,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Nhưng cảm giác đó quá chân thật…</t>
+          <t>Nhưng mọi thứ lại quá chân thật...</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26684,7 +26685,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Not you again…</t>
+          <t>Lại là cậu à…</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26754,7 +26755,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Another one…</t>
+          <t>Lại thêm một cái nữa…</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26824,7 +26825,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Từ Etheric Seaic đến Sonoro, từ thời gian đến không gian…</t>
+          <t>Từ Biển Etheric đến Sonoro, từ thời gian đến không gian…</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26895,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Cảm ơn, but I'm good…</t>
+          <t>Cảm ơn, nhưng tôi ổn rồi…</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26965,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Garden Lời Hứa—</t>
+          <t>Vườn Lời Hứa—</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27035,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Trong câu chuyện này, không có những cuộc phiêu lưu ly kỳ</t>
+          <t>Trong câu chuyện này, chẳng có cuộc phiêu lưu ly kỳ nào cả.</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27105,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Chuyện này không xảy ra vào một thời nào đó xa xưa</t>
+          <t>Chuyện này không phải xảy ra ngày xửa ngày xưa đâu.</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27175,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Thay vào đó, nó diễn ra trong một căn phòng nhỏ</t>
+          <t>Thay vào đó, nó nằm trong một căn phòng nhỏ</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27245,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Đóng vai Wooly Warrior</t>
+          <t>Đóng vai Chiến Binh Lông Xù</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27315,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Nó cũng diễn ra trong một nhà hát</t>
+          <t>Chuyện này cũng xảy ra trong một nhà hát</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27385,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Tấm màn nhấc lên, nhạc cất lên</t>
+          <t>Bức màn kéo lên, bản nhạc vang lên</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27454,7 +27455,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Từng chút một, Wooly Kingdom trở nên chân thật</t>
+          <t>Từng chút một, Vương Quốc Lông Xù dần thành hiện thực</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27524,7 +27525,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Đầu tiên, cô bé leo lên ngọn núi cao nhất</t>
+          <t>Đầu tiên, cô ấy leo lên ngọn núi cao nhất.</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27594,7 +27595,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Nhưng thực ra là để cô bé chứng tỏ lòng dũng cảm của mình</t>
+          <t>Nhưng thực ra là để cô bé chứng tỏ mình dũng cảm đấy.</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27665,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Wooly Warrior cũng tìm kiếm trên mọi bãi biển</t>
+          <t>Chiến Binh Len cũng lùng sục khắp các bãi biển</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27735,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Mẹ cô bé đã ghi lại tất cả những cuộc phiêu lưu của Wooly Warrior</t>
+          <t>Mẹ cô đã ghi lại tất cả những cuộc phiêu lưu của Wooly Warrior.</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27804,7 +27805,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Và những câu chuyện ngày càng dài hơn</t>
+          <t>Và những câu chuyện cứ thế dài thêm mãi</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27874,7 +27875,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Họ thậm chí còn biểu diễn vở kịch ở nhiều thành phố</t>
+          <t>Họ thậm chí còn biểu diễn vở kịch này ở nhiều thành phố khác nhau.</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27944,7 +27945,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>The show ended</t>
+          <t>Màn trình diễn đã kết thúc</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28015,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Và đó không phải là nơi nào đó xa xôi</t>
+          <t>Và nó không ở đâu xa xôi cả</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28085,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Mỗi đêm, có một cô bé</t>
+          <t>Mỗi đêm, có một bé gái...</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28155,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Cô bé chơi trò chơi với mẹ mình</t>
+          <t>Cô bé chơi đùa cùng mẹ mình</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28225,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Cùng nhau, cô bé và mẹ tạo ra câu chuyện này đến câu chuyện khác về lòng dũng cảm và hy vọng</t>
+          <t>Mẹ và con gái cùng nhau viết nên câu chuyện này đến câu chuyện khác về lòng dũng cảm và hy vọng.</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28295,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Mỗi ngày, cô bé ngồi dưới sân khấu</t>
+          <t>Ngày nào cô bé cũng ngồi dưới sân khấu...</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28365,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Cô bé quan sát mẹ mình chuẩn bị mọi thứ</t>
+          <t>Cô bé nhìn mẹ mình chuẩn bị mọi thứ.</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28434,7 +28435,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Đưa Wooly Kingdom từ câu chuyện vào đời thực</t>
+          <t>Đưa Vương Quốc Lông Xù từ truyện cổ tích vào đời thực</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28504,7 +28505,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Và Wooly Warrior bắt đầu cuộc phiêu lưu của mình</t>
+          <t>Và Chiến Binh Lông Xù lên đường phiêu lưu</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28575,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Tìm kiếm thanh kiếm huyền thoại có thể chẻ núi tách biển</t>
+          <t>Tìm thanh kiếm huyền thoại có thể chẻ núi tách biển</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28645,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Hộp dụng cụ thực ra nằm trên kệ cao nhất</t>
+          <t>Hộp dụng cụ lại nằm trên kệ cao nhất ấy.</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28715,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Tìm kiếm khắp nơi để tìm Shield Đức Tin có thể đương đầu với mọi cơn bão</t>
+          <t>Đi khắp nơi tìm Khiên Đức Tin có thể đương đầu bất kỳ bão tố nào</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28784,7 +28785,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Nhà cô bé có rất nhiều ngóc ngách, sau tất cả</t>
+          <t>Nhà cô ấy vốn có nhiều ngóc ngách mà</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28855,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Chiếc kẹo mâm xôi mẹ cô bé giấu có thể ở bất cứ đâu</t>
+          <t>Kẹo mâm xôi mà mẹ cô giấu có thể ở bất cứ đâu.</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28924,7 +28925,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Vương quốc Len vì thế ngày càng lớn mạnh</t>
+          <t>Vậy là Vương Quốc Cừu Trắng ngày càng lớn mạnh...</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28995,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Nhưng mẹ của cô bé ngày càng ốm nặng</t>
+          <t>Nhưng mẹ của cô bé ngày càng ốm nặng hơn...</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29064,7 +29065,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>At the last show</t>
+          <t>Trong đêm diễn cuối</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29134,7 +29135,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Ngay trước khi Chiến binh Len nhận được Wreath Hy Vọng</t>
+          <t>Ngay trước khi Wooly Warrior đoạt được Vòng Hoa Hy Vọng</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29204,7 +29205,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>(Give her a pink flower)</t>
+          <t>(Tặng cô ấy một bông hoa hồng)</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29275,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>(Give her a blue flower)</t>
+          <t>(Tặng cô ấy một bông hoa xanh)</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29345,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Trước khi lên đường thực hiện nhiệm vụ, Tiên Mây sẽ hỏi họ:</t>
+          <t>Trước khi lên đường thực hiện nhiệm vụ, Tiên Nữ Mây sẽ hỏi họ:</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29415,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Tiên Mây vô cùng bối rối trước câu trả lời này, tiếp tục hỏi:</t>
+          <t>Mây Tiên vô cùng bối rối trước câu trả lời này, rồi tiếp tục hỏi:</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29485,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Mẹ à, con có quá nhiều điều muốn nói với mẹ…</t>
+          <t>Mẹ ơi, con có bao nhiêu điều muốn kể cho mẹ nghe…</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29555,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Nhờ những điều ước của các chiến binh dũng cảm</t>
+          <t>Vì nguyện vọng của những chiến binh dũng cảm</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29625,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>At last, ngươi đã trở về…</t>
+          <t>Cuối cùng, ngươi đã trở lại…</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29695,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>It's already spread this far…</t>
+          <t>Nó đã lan xa đến thế này rồi…</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29765,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Còn về thông tin ngươi tìm kiếm—</t>
+          <t>Còn thông tin mà cậu tìm kiếm...</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29834,7 +29835,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Có vẻ như nó cũng được dùng để ghi lại những tần số bất thường ở Thành phố Cảng Guixu…</t>
+          <t>Có vẻ như nó từng được dùng để ghi lại những tần số bất thường ở Thành phố Cảng Guixu…</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29904,7 +29905,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Bạn kể cho Aalto về người bạn đã gặp trên bãi biển…</t>
+          <t>Bạn kể cho Aalto nghe về người bạn đã gặp trên bãi biển…</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29975,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Bạn kể cho Monica những gì đã xảy ra ở Thành phố Cảng Guixu…</t>
+          <t>Bạn kể cho Monica nghe chuyện đã xảy ra ở Thành phố Cảng Guixu…</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30045,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Những Người Mang Hoa ấy đã không hi sinh vô ích…</t>
+          <t>Những người Mang Hoa kia đã không hy sinh vô ích…</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30115,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Vậy là điều này có liên quan đến tần số bất thường đó…</t>
+          <t>Vậy là chuyện này có liên quan đến tần số bất thường đó...</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30184,7 +30185,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Nếu cô ấy đang cư trú trong tần số bất thường đó…</t>
+          <t>Nếu cô ấy đang trú ngụ trong tần số dị thường đó…</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30394,7 +30395,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>What happened in that city…</t>
+          <t>Thành phố đó đã xảy ra chuyện gì…</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30465,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Ta biết Black Shores chứa đựng nhiều câu trả lời cho ngươi—ký ức, quá khứ của ngươi…</t>
+          <t>Ta biết Bờ Biển Đen chứa đựng nhiều câu trả lời cho ngươi—những ký ức, quá khứ của ngươi…</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30534,8 +30535,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Midnight Rangers đang chuẩn bị bảo vệ Thành phố Cảng Guixu, và…
-NAME_TITLE_002374:::Với quyền truy cập cao hơn, ngươi có thể tìm ra câu trả lời mà ngươi đang tìm kiếm…</t>
+          <t>Biệt Đội Midnight Rangers đang chuẩn bị bảo vệ Thành Phố Cảng Guixu, và…</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30605,7 +30605,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>So…</t>
+          <t>Vậy…</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30815,7 +30815,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Lalala, happy watering…</t>
+          <t>Lalala, tưới nước vui vẻ...</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30885,7 +30885,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Lớn lên và nở hoa nào, những bông hoa nhỏ đáng yêu của ta…</t>
+          <t>Lớn lên và nở rộ đi, những bông hoa bé nhỏ ngọt ngào của ta…</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30955,7 +30955,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Có vẻ như Hệ thống Tethys đang giấu gì đó khỏi cậu…</t>
+          <t>Có vẻ như Hệ Tethys đang giấu cậu điều gì đó...</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31025,7 +31025,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>(Try to touch a key)</t>
+          <t>(Thử ấn một phím xem.)</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31165,7 +31165,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>(Keep touching the keys)</t>
+          <t>Tiếp tục gõ phím đi.</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31305,7 +31305,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>(Keep touching the keys)</t>
+          <t>Tiếp tục gõ phím đi.</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31375,7 +31375,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Cứ như thế này, bày tỏ tâm tư qua âm nhạc…</t>
+          <t>Giống như thế này, bày tỏ tâm tư qua âm nhạc...</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31445,7 +31445,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>I… I'm so sleepy…</t>
+          <t>Tôi… buồn ngủ quá…</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31515,7 +31515,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Nếu không có cậu dẫn đầu, chúng ta đã khó mà vượt qua được—</t>
+          <t>Nếu không có cậu dẫn đầu, chúng ta đã chẳng thể nào vượt qua được—</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31585,7 +31585,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Người thầy của tôi… người mà tôi đi theo…</t>
+          <t>Người thầy của ta… người mà ta đi theo…</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31725,7 +31725,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Tôi không nhớ gì cả…</t>
+          <t>Tôi không nhớ gì về chuyện này cả…</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31795,7 +31795,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Bạn mean…</t>
+          <t>Ý cậu...</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31865,7 +31865,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Ui, vẫn phải đợi cả tuần nữa mới được nhận tín dụng vỏ sò…</t>
+          <t>Ôi, còn phải đợi cả tuần nữa mới được nhận shell credits...</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31935,7 +31935,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Y-yes…</t>
+          <t>V-vâng...</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32005,7 +32005,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Thường thì chẳng ai đến Ngân hàng Sự sống ngoại trừ Shorekeeper…</t>
+          <t>Thường thì chẳng ai đến Ngân Hàng Sự Sống ngoài Người Gác Bờ đâu…</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32075,7 +32075,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Hy vọng tôi sẽ sớm có cơ hội gặp cô ấy…</t>
+          <t>Ta mong sớm có cơ hội gặp cô ấy…</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32145,7 +32145,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Astral Modulator, Người dẫn dắt nền văn minh, Kiến trúc sư của Bờ biển Đen…</t>
+          <t>Bộ Điều Tần Tinh Tú, Người Dẫn Dắt Văn Minh, Bậc Thầy Bờ Đen…</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32215,7 +32215,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>(Reach out your hand)</t>
+          <t>Đưa tay ra.</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32285,7 +32285,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>It razes cities</t>
+          <t>Nó thiêu rụi các thành phố.</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32355,7 +32355,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>topples towers</t>
+          <t>Làm đổ sập những tòa tháp</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32565,7 +32565,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>In other words—</t>
+          <t>Nói cách khác—</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32635,7 +32635,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>R… Run…</t>
+          <t>Ch… Chạy đi…</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32705,7 +32705,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>The building collapsed…</t>
+          <t>Tòa nhà đổ sập rồi…</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32775,7 +32775,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Tất cả đều bị mắc kẹt… Hoàn toàn tắc nghẽn…</t>
+          <t>Tất cả đều bị kẹt cứng… Chẳng nhúc nhích được tí nào…</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32845,7 +32845,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Remember… Remember it all…</t>
+          <t>Nhớ đi… Hãy nhớ tất cả…</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32915,7 +32915,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Điều ngươi tìm kiếm… đang ở trên cô gái đó…</t>
+          <t>Thứ cậu tìm kiếm… đang ở trên người cô gái ấy…</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32985,7 +32985,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>What…</t>
+          <t>Cái gì…</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33055,7 +33055,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>What happened here…</t>
+          <t>Chuyện gì đã xảy ra ở đây…</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33125,7 +33125,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Ta cảm thấy có điều gì đó còn ẩn giấu hơn những gì mắt thấy…</t>
+          <t>Ta cảm thấy có điều gì đó không đơn giản như vẻ ngoài…</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33265,7 +33265,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Bạn are…</t>
+          <t>Ngươi là...</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33335,7 +33335,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>I've felt this way before…</t>
+          <t>Ta đã từng cảm thấy như thế này rồi…</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33405,7 +33405,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Nghe có vẻ hơi… thú tính quá nhỉ…</t>
+          <t>Nghe có vẻ... quá thú tính nhỉ…</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33475,7 +33475,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>This Blake Bloom is…</t>
+          <t>Blake Bloom này...</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33545,7 +33545,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Cách ngươi chiến đấu thật khiến trái tim ta đập rộn ràng… Sức mạnh như vậy, sự sống động như vậy…</t>
+          <t>Cách cậu chiến đấu khiến tim tao đập rộn ràng... Sức mạnh, sự mãnh liệt như vậy...</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33615,7 +33615,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Ui, ước gì ta là người được khiêu vũ điệu valse chết chóc, đẫm máu và tuyệt đẹp này cùng ngươi…</t>
+          <t>Ước gì người khiêu vũ điệu valse chết chóc, đẫm máu mà đẹp đẽ này là tớ…</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33685,7 +33685,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Ngươi nói ký ức của ngươi bị phong ấn bởi Quý cô Flora…</t>
+          <t>Ngươi nói ký ức của ngươi đã bị Lady Flora phong ấn…</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33755,7 +33755,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Tất cả những con đường trên bầu trời sao đều hội tụ về một điểm cuối duy nhất, vậy nên—</t>
+          <t>Mọi con đường giữa các vì sao đều dẫn về một điểm cuối duy nhất, vậy nên—</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33895,7 +33895,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Camellya and I got separated…</t>
+          <t>Tớ và Camellya bị lạc nhau rồi…</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33965,7 +33965,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Không, I remember…</t>
+          <t>Không, tôi nhớ...</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34105,7 +34105,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>It's you…</t>
+          <t>Là cậu…</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34175,7 +34175,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Petalfall Village…</t>
+          <t>Làng Hoa Rơi…</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34245,7 +34245,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>I see… Ah, it's over…</t>
+          <t>Ra là vậy… À, kết thúc rồi.</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34315,7 +34315,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Dường như ta… đã gặp ngươi… từ rất lâu rồi…</t>
+          <t>Ta dường như… đã gặp ngươi… từ rất lâu rồi…</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34385,7 +34385,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Ta đã cố sửa chữa nó, nhưng không thể khôi phục được nhiều dữ liệu… Ta chỉ lấy được đoạn ghi âm bị hỏng này:</t>
+          <t>Tao đã cố sửa nó, nhưng không thể khôi phục được nhiều dữ liệu… Chỉ còn lại đoạn ghi âm hỏng này thôi:</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34455,7 +34455,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Ai đó đã xóa sạch mọi thứ về Quý cô Flora…</t>
+          <t>Có kẻ đã xóa sạch mọi dấu vết về Quý cô Flora...</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34525,7 +34525,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Thật không may, Quý cô Flora đã mất tích gần hai thập kỷ rồi…</t>
+          <t>Thật tiếc, Quý cô Flora đã mất tích gần hai thập kỷ rồi…</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34595,7 +34595,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Hmm…</t>
+          <t>Hừm…</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34665,7 +34665,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Ta rất vui, thật sự, thật sự vui vì những dây leo của ta cảm thấy nhẹ nhàng đến thế…</t>
+          <t>Mình vui quá, vui lắm luôn ấy... những dây leo của mình nhẹ bẫng đi...</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34735,7 +34735,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Bông hoa này dành tặng ngươi, để bày tỏ…</t>
+          <t>Bông hoa này tặng em, để bày tỏ...</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34805,7 +34805,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Bạn've lost your memory too…</t>
+          <t>Ngươi cũng mất trí nhớ rồi à…</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34945,7 +34945,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>I see… (static)… something… deep…</t>
+          <t>Ra là vậy… *tĩnh điện*… có gì đó… sâu thẳm…</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35015,7 +35015,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>I'll catch… then meet me…</t>
+          <t>Tao sẽ bắt... rồi gặp nhau...</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35085,7 +35085,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Nếu ta không quay trở lại Black Shores và trở thành Người Mang Hoa một lần nữa…</t>
+          <t>Nếu không quay về Bờ Đen và trở lại làm Người Gieo Mầm...</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35155,7 +35155,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Sau ngần ấy năm, {Male=anh;Female=cô} ấy vẫn đưa ra lựa chọn đó…</t>
+          <t>Sau bao năm tháng, {Male=he;Female=she} vẫn đưa ra lựa chọn đó…</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35225,7 +35225,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Như hoa khát nước, như thú thèm thịt…</t>
+          <t>Như hoa khát nước, như thú đói thịt...</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35295,7 +35295,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Ta có thể sẽ quên ngươi, hết lần này đến lần khác…</t>
+          <t>Ta có thể sẽ quên cậu, hết lần này đến lần khác…</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35365,7 +35365,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Nhưng miễn là ta còn bản năng…</t>
+          <t>Nhưng miễn là bản năng của ta vẫn còn...</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35435,7 +35435,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Không ngạc nhiên khi ta cảm thấy quen thuộc khi lần đầu gặp ngươi bên ngoài Jinzhou…</t>
+          <t>Thảo nào lần đầu gặp cậu ngoài Jinzhou, mình đã thấy quen thuộc đến lạ…</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
